--- a/docs/开发相关/详细需求文档.xlsx
+++ b/docs/开发相关/详细需求文档.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\Razel\Razel\VoicePilot\docs\开发相关\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC2B9C0A-FC5D-4948-970E-487085A7A8AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="2460" yWindow="2865" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="我需要基于大模型开发一个用语音对话的方式来控制电脑的应用，比如" sheetId="1" r:id="rId4"/>
+    <sheet name="我需要基于大模型开发一个用语音对话的方式来控制电脑的应用，比如" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="70">
   <si>
     <t>ID</t>
   </si>
@@ -37,15 +46,9 @@
     <t>基础交互</t>
   </si>
   <si>
-    <t>支持语音唤醒：应用在后台运行时，能通过特定的唤醒词（如“你好，助手”）激活并进入聆听状态。</t>
-  </si>
-  <si>
     <t>高</t>
   </si>
   <si>
-    <t>这是实现“语音对话”的入口。需要低功耗的本地唤醒词模型。</t>
-  </si>
-  <si>
     <t>连续对话能力：支持上下文理解，用户可以进行多轮对话。例如，用户说“播放音乐”，应用问“想听什么歌？”，用户回答“周杰伦的稻香”。</t>
   </si>
   <si>
@@ -88,12 +91,6 @@
     <t>语音识别 (ASR)</t>
   </si>
   <si>
-    <t>实时语音转文字：在用户说话时，能够低延迟地将语音流转换为文字，并在界面上实时显示。</t>
-  </si>
-  <si>
-    <t>低延迟对于交互体验至关重要。可以选择本地模型或云服务。</t>
-  </si>
-  <si>
     <t>高识别准确率：在常规环境下，对普通话的识别准确率应达到较高水平（例如95%以上），以减少因识别错误导致的交互失败。</t>
   </si>
   <si>
@@ -109,9 +106,6 @@
     <t>声音的自然度直接影响用户体验。</t>
   </si>
   <si>
-    <t>可配置音色/语速：用户可以在设置中选择不同的发音人（男声/女声/童声等）和调整语速。</t>
-  </si>
-  <si>
     <t>提升个性化体验。</t>
   </si>
   <si>
@@ -160,21 +154,12 @@
     <t>工具库/能力接口</t>
   </si>
   <si>
-    <t>定义与实现原子能力：需要用您的主力语言（C++）封装一系列与操作系统交互的函数，作为 LLM 可调用的“工具”。</t>
-  </si>
-  <si>
     <t>例如：openApplication(string path), setVolume(int level), typeText(string text), searchWeb(string query) 等。</t>
   </si>
   <si>
     <t>安全与权限</t>
   </si>
   <si>
-    <t>建立安全沙箱：LLM 生成的指令必须在一个受限的环境中执行。严禁 LLM 直接生成和执行任意代码或Shell命令，只能调用您预先定义好的安全函数。</t>
-  </si>
-  <si>
-    <t>极高</t>
-  </si>
-  <si>
     <t>安全是第一位。防止恶意或错误的指令对系统造成破坏。</t>
   </si>
   <si>
@@ -211,9 +196,6 @@
     <t>设置界面</t>
   </si>
   <si>
-    <t>提供配置选项：允许用户进行基本设置，如选择麦克风/扬声器设备、设置唤醒词、配置 TTS 音色、查看可用的指令列表等。</t>
-  </si>
-  <si>
     <t>提升应用的可用性和灵活性。</t>
   </si>
   <si>
@@ -226,41 +208,296 @@
     <t>低延迟响应：从用户说完话到系统给出语音回应的总时长应尽可能短（理想情况在2-3秒内）。</t>
   </si>
   <si>
-    <t>性能是语音助手的生命线。</t>
-  </si>
-  <si>
-    <t>低资源占用：应用在待机（等待唤醒词）状态下，CPU和内存占用应极低，不影响用户正常使用电脑。</t>
-  </si>
-  <si>
     <t>可靠性</t>
   </si>
   <si>
     <t>稳定的运行：应用应能长时间稳定运行，不易崩溃，并有合理的错误处理和恢复机制。</t>
   </si>
   <si>
-    <t>隐私</t>
-  </si>
-  <si>
-    <t>明确的隐私策略：应明确告知用户语音数据的处理方式（例如，是否上传云端进行处理），并提供选项让用户管理自己的数据。</t>
-  </si>
-  <si>
-    <t>保护用户隐私至关重要。</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提供配置选项：允许用户进行基本设置，如选择麦克风</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>扬声器设备、设置唤醒词、配置</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> TTS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>音色、查看可用的指令列表等。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>低</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>高</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>可配置音色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>语速：用户可以在设置中选择不同的发音人和调整语速。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>定义与实现原子能力：需要封装一系列与操作系统交互的函数，作为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> LLM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>可调用的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>工具</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>建立安全沙箱：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">LLM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>生成的指令必须在一个受限的环境中执行。严禁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> LLM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>直接生成和执行任意代码或</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Shell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>命令，只能调用预先定义好的安全函数。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -269,36 +506,46 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -488,22 +735,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="7.38"/>
-    <col customWidth="1" min="2" max="2" width="22.13"/>
-    <col customWidth="1" min="4" max="4" width="119.25"/>
+    <col min="1" max="1" width="7.42578125" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" customWidth="1"/>
+    <col min="4" max="4" width="119.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -523,9 +774,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" ht="12.75">
       <c r="A2" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -534,265 +785,268 @@
         <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>1.2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>1.3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>1.4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="12.75">
+      <c r="A7" s="1">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="16.5">
+      <c r="A9" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1">
-        <v>2.1</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
-        <v>2.2</v>
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>3.2</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="1">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="16.5">
       <c r="A14" s="1">
-        <v>3.2</v>
+        <v>4</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="16.5">
       <c r="A15" s="1">
-        <v>3.3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>9</v>
+      <c r="D15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6">
       <c r="A16" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="B16" s="1" t="s">
+        <v>4.2</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="1" t="s">
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="1">
+        <v>5</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1">
-        <v>4.1</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>51</v>
@@ -801,149 +1055,87 @@
         <v>52</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F17" s="1" t="s">
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1">
-        <v>4.2</v>
-      </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" s="1" t="s">
+    </row>
+    <row r="19" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A19" s="1">
+        <v>5.2</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="B19" s="1" t="s">
+      <c r="D19" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="1" t="s">
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="1">
+        <v>6</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1">
-        <v>5.1</v>
-      </c>
-      <c r="C20" s="1" t="s">
+      <c r="E20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1">
-        <v>5.2</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="E21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1">
-        <v>6.1</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1">
-        <v>6.2</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1">
-        <v>6.3</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>77</v>
-      </c>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>